--- a/Excel/SoulBoneConfig.xlsx
+++ b/Excel/SoulBoneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -35,6 +35,12 @@
     <t>Name</t>
   </si>
   <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
+  </si>
+  <si>
     <t>AttrIdList</t>
   </si>
   <si>
@@ -102,6 +108,54 @@
   </si>
   <si>
     <t>14,15,16,18,20,19,24,2001</t>
+  </si>
+  <si>
+    <t>八蛛魂骨·极</t>
+  </si>
+  <si>
+    <t>智慧头骨·极</t>
+  </si>
+  <si>
+    <t>蓝银皇骨·极</t>
+  </si>
+  <si>
+    <t>柔骨兔骨·极</t>
+  </si>
+  <si>
+    <t>邪魔腿骨·极</t>
+  </si>
+  <si>
+    <t>泰坦巨猿骨·极</t>
+  </si>
+  <si>
+    <t>天青牛蟒骨·极</t>
+  </si>
+  <si>
+    <t>魔鲸王骨·极</t>
+  </si>
+  <si>
+    <t>八蛛魂骨·道</t>
+  </si>
+  <si>
+    <t>智慧头骨·道</t>
+  </si>
+  <si>
+    <t>蓝银皇骨·道</t>
+  </si>
+  <si>
+    <t>柔骨兔骨·道</t>
+  </si>
+  <si>
+    <t>邪魔腿骨·道</t>
+  </si>
+  <si>
+    <t>泰坦巨猿骨·道</t>
+  </si>
+  <si>
+    <t>天青牛蟒骨·道</t>
+  </si>
+  <si>
+    <t>魔鲸王骨·道</t>
   </si>
 </sst>
 </file>
@@ -1068,33 +1122,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.8166666666667" style="2" customWidth="1"/>
-    <col min="8" max="16366" width="9" style="2"/>
-    <col min="16367" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5044247787611" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.9380530973451" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5398230088496" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.283185840708" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.6283185840708" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.8141592920354" style="2" customWidth="1"/>
+    <col min="10" max="16368" width="9" style="2"/>
+    <col min="16369" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1112,12 +1168,18 @@
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1131,389 +1193,753 @@
       <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:7">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="1">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>80</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1">
         <v>8101</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>80</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1">
         <v>8102</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="1">
+        <v>17</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>80</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1">
         <v>8103</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>80</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1">
         <v>8104</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>80</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1">
         <v>8105</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>80</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1">
         <v>8106</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="1">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>80</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1">
         <v>8107</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>80</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:9">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="4">
+        <v>81</v>
+      </c>
+      <c r="F14" s="4">
+        <v>160</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8101</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:9">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="4">
+        <v>81</v>
+      </c>
+      <c r="F15" s="4">
+        <v>160</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:9">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="4">
+        <v>81</v>
+      </c>
+      <c r="F16" s="4">
+        <v>160</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1">
+        <v>8103</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:9">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="4">
+        <v>81</v>
+      </c>
+      <c r="F17" s="4">
+        <v>160</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1">
+        <v>8104</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:9">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="4">
+        <v>81</v>
+      </c>
+      <c r="F18" s="4">
+        <v>160</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="4">
+        <v>81</v>
+      </c>
+      <c r="F19" s="4">
+        <v>160</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1">
+        <v>8106</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="4">
+        <v>81</v>
+      </c>
+      <c r="F20" s="4">
+        <v>160</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1">
+        <v>8107</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:9">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="4">
+        <v>81</v>
+      </c>
+      <c r="F21" s="4">
+        <v>160</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:9">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="4">
+        <v>81</v>
+      </c>
+      <c r="F22" s="4">
+        <v>160</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1">
+        <v>8101</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:9">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="4">
+        <v>161</v>
+      </c>
+      <c r="F23" s="4">
+        <v>240</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:9">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="4">
+        <v>161</v>
+      </c>
+      <c r="F24" s="4">
+        <v>240</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1">
+        <v>8103</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:9">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="4">
+        <v>161</v>
+      </c>
+      <c r="F25" s="4">
+        <v>240</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8104</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:9">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="4">
+        <v>161</v>
+      </c>
+      <c r="F26" s="4">
+        <v>240</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1">
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:9">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="4">
+        <v>161</v>
+      </c>
+      <c r="F27" s="4">
+        <v>240</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8106</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:9">
+      <c r="C28" s="1">
         <v>23</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="4">
+        <v>161</v>
+      </c>
+      <c r="F28" s="4">
+        <v>240</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8107</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:9">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="4">
+        <v>161</v>
+      </c>
+      <c r="F29" s="4">
+        <v>240</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1">
         <v>8108</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="5:6">
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" customHeight="1" spans="5:6">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" customHeight="1" spans="5:6">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="5:6">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:6">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="5:6">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:6">
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:6">
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="5:6">
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:6">
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:6">
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="5:6">
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="5:6">
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="5:6">
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="5:6">
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="5:6">
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="5:6">
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="5:6">
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="5:6">
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="5:6">
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="5:6">
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="5:6">
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="5:6">
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="5:6">
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="5:6">
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="5:6">
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="5:6">
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="5:6">
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="5:6">
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="5:6">
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="5:6">
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="5:6">
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="5:6">
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="5:6">
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="5:6">
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="5:6">
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="5:6">
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="5:6">
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="5:6">
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="5:6">
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="5:6">
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="5:6">
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="5:6">
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="5:6">
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="5:6">
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="5:6">
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="5:6">
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="5:6">
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="5:6">
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="5:6">
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-    </row>
-    <row r="65" customHeight="1" spans="5:6">
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" customHeight="1" spans="5:6">
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-    </row>
-    <row r="67" customHeight="1" spans="5:6">
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-    </row>
-    <row r="68" customHeight="1" spans="5:6">
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" customHeight="1" spans="5:6">
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" customHeight="1" spans="5:6">
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
+    <row r="30" customHeight="1" spans="7:8">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="7:8">
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="7:8">
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="7:8">
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="7:8">
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="7:8">
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="7:8">
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="7:8">
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="7:8">
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="7:8">
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="7:8">
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="7:8">
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="7:8">
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="7:8">
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="7:8">
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="7:8">
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="7:8">
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="7:8">
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="7:8">
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="7:8">
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="7:8">
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="7:8">
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="7:8">
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="7:8">
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="7:8">
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="7:8">
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="7:8">
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="7:8">
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="7:8">
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customHeight="1" spans="7:8">
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customHeight="1" spans="7:8">
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" customHeight="1" spans="7:8">
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="7:8">
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" customHeight="1" spans="7:8">
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" customHeight="1" spans="7:8">
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" customHeight="1" spans="7:8">
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" customHeight="1" spans="7:8">
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" customHeight="1" spans="7:8">
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" customHeight="1" spans="7:8">
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" customHeight="1" spans="7:8">
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 C3:D5 G3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SoulBoneConfig.xlsx
+++ b/Excel/SoulBoneConfig.xlsx
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Sid</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -113,49 +116,97 @@
     <t>八蛛魂骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2003,2002</t>
+  </si>
+  <si>
+    <t>10,10,10,1,1,0.5,0.5,0.1,0.08</t>
+  </si>
+  <si>
     <t>智慧头骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2004,2003</t>
+  </si>
+  <si>
     <t>蓝银皇骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2002,2001</t>
+  </si>
+  <si>
     <t>柔骨兔骨·极</t>
   </si>
   <si>
     <t>邪魔腿骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2005,2003</t>
+  </si>
+  <si>
     <t>泰坦巨猿骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2003,2001</t>
+  </si>
+  <si>
     <t>天青牛蟒骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2006,2003</t>
+  </si>
+  <si>
     <t>魔鲸王骨·极</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2001,2003</t>
+  </si>
+  <si>
     <t>八蛛魂骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2003,2002,2001</t>
+  </si>
+  <si>
+    <t>10,10,10,1,1,0.5,0.5,0.1,0.08,0.07</t>
+  </si>
+  <si>
     <t>智慧头骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2004,2003,2001</t>
+  </si>
+  <si>
     <t>蓝银皇骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2002,2001,2003</t>
+  </si>
+  <si>
     <t>柔骨兔骨·道</t>
   </si>
   <si>
     <t>邪魔腿骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2005,2003,2001</t>
+  </si>
+  <si>
     <t>泰坦巨猿骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2003,2001,2002</t>
+  </si>
+  <si>
     <t>天青牛蟒骨·道</t>
   </si>
   <si>
+    <t>14,15,16,18,20,19,24,2006,2003,2001</t>
+  </si>
+  <si>
     <t>魔鲸王骨·道</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2001,2003,2010</t>
   </si>
 </sst>
 </file>
@@ -1122,35 +1173,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5044247787611" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.9380530973451" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5398230088496" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.283185840708" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.6283185840708" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18.8141592920354" style="2" customWidth="1"/>
-    <col min="10" max="16368" width="9" style="2"/>
-    <col min="16369" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5044247787611" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.9380530973451" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5398230088496" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.8141592920354" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27.8849557522124" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.8141592920354" style="2" customWidth="1"/>
+    <col min="11" max="16369" width="9" style="2"/>
+    <col min="16370" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1174,12 +1225,15 @@
       <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1199,747 +1253,825 @@
       <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>80</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1">
         <v>8101</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>80</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4">
-        <v>80</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>8102</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
         <v>80</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="1">
+        <v>19</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="1">
         <v>8103</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
         <v>80</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="1">
         <v>8104</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
         <v>80</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="1">
+        <v>22</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="1">
         <v>8105</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
+      <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
         <v>80</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="1">
         <v>8106</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
+      <c r="D12" s="1">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
         <v>80</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="1">
+        <v>25</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="1">
         <v>8107</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
+      <c r="D13" s="1">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
         <v>80</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="1">
+        <v>27</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="1">
         <v>8108</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:9">
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="4">
         <v>81</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>160</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="1">
+        <v>29</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="1">
         <v>8101</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:9">
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="4">
         <v>81</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>160</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="1">
+        <v>32</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="1">
         <v>8102</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:9">
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="4">
         <v>81</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>160</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="1">
+        <v>34</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="1">
         <v>8103</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:9">
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="1">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4">
+        <v>81</v>
+      </c>
+      <c r="G17" s="4">
+        <v>160</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="4">
-        <v>81</v>
-      </c>
-      <c r="F17" s="4">
-        <v>160</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>8104</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:9">
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="1">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="4">
         <v>81</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>160</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="1">
+        <v>37</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="1">
         <v>8105</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:9">
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="4">
         <v>81</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>160</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="1">
+        <v>39</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1">
         <v>8106</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:9">
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="1">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="4">
         <v>81</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>160</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="H20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="1">
+        <v>41</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="1">
         <v>8107</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:9">
+    <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D21" s="1">
+        <v>8</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="4">
         <v>81</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="4">
         <v>160</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="1">
+        <v>43</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="1">
         <v>8108</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:9">
+    <row r="22" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="4">
-        <v>81</v>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="F22" s="4">
-        <v>160</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>13</v>
+        <v>161</v>
+      </c>
+      <c r="G22" s="4">
+        <v>240</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="1">
+        <v>45</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="1">
         <v>8101</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:9">
+    <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="4">
         <v>161</v>
       </c>
-      <c r="F23" s="4">
+      <c r="G23" s="4">
         <v>240</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="H23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="1">
+        <v>48</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="1">
         <v>8102</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:9">
+    <row r="24" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="4">
         <v>161</v>
       </c>
-      <c r="F24" s="4">
+      <c r="G24" s="4">
         <v>240</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="H24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="1">
+        <v>50</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="1">
         <v>8103</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:9">
+    <row r="25" customHeight="1" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="4">
         <v>161</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>240</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="1">
+        <v>45</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="1">
         <v>8104</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:9">
+    <row r="26" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="4">
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="4">
         <v>161</v>
       </c>
-      <c r="F26" s="4">
+      <c r="G26" s="4">
         <v>240</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="H26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="1">
+        <v>53</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="1">
         <v>8105</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:9">
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="4">
         <v>161</v>
       </c>
-      <c r="F27" s="4">
+      <c r="G27" s="4">
         <v>240</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="1">
+        <v>55</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" s="1">
         <v>8106</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:9">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>23</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="D28" s="1">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="4">
         <v>161</v>
       </c>
-      <c r="F28" s="4">
+      <c r="G28" s="4">
         <v>240</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="1">
+        <v>57</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="1">
         <v>8107</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:9">
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="D29" s="1">
+        <v>8</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="4">
         <v>161</v>
       </c>
-      <c r="F29" s="4">
+      <c r="G29" s="4">
         <v>240</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="1">
+        <v>59</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" s="1">
         <v>8108</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="7:8">
-      <c r="G30" s="1"/>
+    <row r="30" customHeight="1" spans="8:9">
       <c r="H30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="7:8">
-      <c r="G31" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="8:9">
       <c r="H31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="7:8">
-      <c r="G32" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="8:9">
       <c r="H32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="7:8">
-      <c r="G33" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="8:9">
       <c r="H33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="7:8">
-      <c r="G34" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="8:9">
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="7:8">
-      <c r="G35" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="8:9">
       <c r="H35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="7:8">
-      <c r="G36" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="8:9">
       <c r="H36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="7:8">
-      <c r="G37" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="8:9">
       <c r="H37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="7:8">
-      <c r="G38" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="8:9">
       <c r="H38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="7:8">
-      <c r="G39" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="8:9">
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="7:8">
-      <c r="G40" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="8:9">
       <c r="H40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="7:8">
-      <c r="G41" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="8:9">
       <c r="H41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="7:8">
-      <c r="G42" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="8:9">
       <c r="H42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="7:8">
-      <c r="G43" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="8:9">
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="7:8">
-      <c r="G44" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="8:9">
       <c r="H44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="7:8">
-      <c r="G45" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="8:9">
       <c r="H45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="7:8">
-      <c r="G46" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="8:9">
       <c r="H46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="7:8">
-      <c r="G47" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="8:9">
       <c r="H47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="7:8">
-      <c r="G48" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="8:9">
       <c r="H48" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="7:8">
-      <c r="G50" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="8:9">
       <c r="H50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="7:8">
-      <c r="G51" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="8:9">
       <c r="H51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="7:8">
-      <c r="G52" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="8:9">
       <c r="H52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="7:8">
-      <c r="G53" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="8:9">
       <c r="H53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="7:8">
-      <c r="G54" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="8:9">
       <c r="H54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="7:8">
-      <c r="G55" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="8:9">
       <c r="H55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="7:8">
-      <c r="G56" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="8:9">
       <c r="H56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="7:8">
-      <c r="G57" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="8:9">
       <c r="H57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="7:8">
-      <c r="G58" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="8:9">
       <c r="H58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="7:8">
-      <c r="G59" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="8:9">
       <c r="H59" s="1"/>
-    </row>
-    <row r="60" customHeight="1" spans="7:8">
-      <c r="G60" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" customHeight="1" spans="8:9">
       <c r="H60" s="1"/>
-    </row>
-    <row r="61" customHeight="1" spans="7:8">
-      <c r="G61" s="1"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" customHeight="1" spans="8:9">
       <c r="H61" s="1"/>
-    </row>
-    <row r="62" customHeight="1" spans="7:8">
-      <c r="G62" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" customHeight="1" spans="8:9">
       <c r="H62" s="1"/>
-    </row>
-    <row r="63" customHeight="1" spans="7:8">
-      <c r="G63" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="8:9">
       <c r="H63" s="1"/>
-    </row>
-    <row r="64" customHeight="1" spans="7:8">
-      <c r="G64" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" customHeight="1" spans="8:9">
       <c r="H64" s="1"/>
-    </row>
-    <row r="65" customHeight="1" spans="7:8">
-      <c r="G65" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" customHeight="1" spans="8:9">
       <c r="H65" s="1"/>
-    </row>
-    <row r="66" customHeight="1" spans="7:8">
-      <c r="G66" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" customHeight="1" spans="8:9">
       <c r="H66" s="1"/>
-    </row>
-    <row r="67" customHeight="1" spans="7:8">
-      <c r="G67" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" customHeight="1" spans="8:9">
       <c r="H67" s="1"/>
-    </row>
-    <row r="68" customHeight="1" spans="7:8">
-      <c r="G68" s="1"/>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" customHeight="1" spans="8:9">
       <c r="H68" s="1"/>
-    </row>
-    <row r="69" customHeight="1" spans="7:8">
-      <c r="G69" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" customHeight="1" spans="8:9">
       <c r="H69" s="1"/>
-    </row>
-    <row r="70" customHeight="1" spans="7:8">
-      <c r="G70" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" customHeight="1" spans="8:9">
       <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 F3 E4 F4 E5 F5 C3:D5 G3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SoulBoneConfig.xlsx
+++ b/Excel/SoulBoneConfig.xlsx
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>14</v>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>19</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>14</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>22</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>14</v>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>25</v>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>27</v>
@@ -1504,10 +1504,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G14" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>29</v>
@@ -1530,10 +1530,10 @@
         <v>31</v>
       </c>
       <c r="F15" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G15" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>32</v>
@@ -1556,10 +1556,10 @@
         <v>33</v>
       </c>
       <c r="F16" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G16" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>34</v>
@@ -1582,10 +1582,10 @@
         <v>35</v>
       </c>
       <c r="F17" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G17" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>29</v>
@@ -1608,10 +1608,10 @@
         <v>36</v>
       </c>
       <c r="F18" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G18" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>37</v>
@@ -1634,10 +1634,10 @@
         <v>38</v>
       </c>
       <c r="F19" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G19" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>39</v>
@@ -1660,10 +1660,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G20" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>41</v>
@@ -1686,10 +1686,10 @@
         <v>42</v>
       </c>
       <c r="F21" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G21" s="4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>43</v>
@@ -1712,10 +1712,10 @@
         <v>44</v>
       </c>
       <c r="F22" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G22" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>45</v>
@@ -1738,10 +1738,10 @@
         <v>47</v>
       </c>
       <c r="F23" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G23" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>48</v>
@@ -1764,10 +1764,10 @@
         <v>49</v>
       </c>
       <c r="F24" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G24" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>50</v>
@@ -1790,10 +1790,10 @@
         <v>51</v>
       </c>
       <c r="F25" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G25" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>45</v>
@@ -1816,10 +1816,10 @@
         <v>52</v>
       </c>
       <c r="F26" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G26" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>53</v>
@@ -1842,10 +1842,10 @@
         <v>54</v>
       </c>
       <c r="F27" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G27" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>55</v>
@@ -1868,10 +1868,10 @@
         <v>56</v>
       </c>
       <c r="F28" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G28" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>57</v>
@@ -1894,10 +1894,10 @@
         <v>58</v>
       </c>
       <c r="F29" s="4">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="G29" s="4">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>59</v>

--- a/Excel/SoulBoneConfig.xlsx
+++ b/Excel/SoulBoneConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -207,6 +207,30 @@
   </si>
   <si>
     <t>14,15,16,18,20,19,24,2001,2003,2010</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2003,2002,2001,2013</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2004,2003,2001,2013</t>
+  </si>
+  <si>
+    <t>10,10,10,1,1,0.5,0.5,0.1,0.08,0.07,0.05</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2002,2001,2003,2013</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2005,2003,2001,2013</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2003,2001,2002,2013</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2006,2003,2001,2013</t>
+  </si>
+  <si>
+    <t>14,15,16,18,20,19,24,2001,2003,2010,2013</t>
   </si>
 </sst>
 </file>
@@ -1176,26 +1200,26 @@
   <dimension ref="A1:J70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5044247787611" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.9380530973451" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5398230088496" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.8141592920354" style="2" customWidth="1"/>
-    <col min="9" max="9" width="27.8849557522124" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.8141592920354" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5083333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.9416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5416666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.8166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27.8833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.8166666666667" style="2" customWidth="1"/>
     <col min="11" max="16369" width="9" style="2"/>
     <col min="16370" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
@@ -1285,7 +1309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1311,7 +1335,7 @@
         <v>8101</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1337,7 +1361,7 @@
         <v>8102</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1363,7 +1387,7 @@
         <v>8103</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1389,7 +1413,7 @@
         <v>8104</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1415,7 +1439,7 @@
         <v>8105</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1441,7 +1465,7 @@
         <v>8106</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1467,7 +1491,7 @@
         <v>8107</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1493,7 +1517,7 @@
         <v>8108</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:10">
+    <row r="14" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1519,7 +1543,7 @@
         <v>8101</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:10">
+    <row r="15" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1545,7 +1569,7 @@
         <v>8102</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
+    <row r="16" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1909,79 +1933,255 @@
         <v>8108</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="8:9">
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="8:9">
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="8:9">
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="8:9">
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="8:9">
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:9">
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:9">
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="8:9">
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="8:9">
+    <row r="30" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="4">
+        <v>271</v>
+      </c>
+      <c r="G30" s="4">
+        <v>360</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="1">
+        <v>8101</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="4">
+        <v>271</v>
+      </c>
+      <c r="G31" s="4">
+        <v>360</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="1">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="4">
+        <v>271</v>
+      </c>
+      <c r="G32" s="4">
+        <v>360</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" s="1">
+        <v>8103</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="4">
+        <v>271</v>
+      </c>
+      <c r="G33" s="4">
+        <v>360</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J33" s="1">
+        <v>8104</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>5</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="4">
+        <v>271</v>
+      </c>
+      <c r="G34" s="4">
+        <v>360</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J34" s="1">
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>6</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="4">
+        <v>271</v>
+      </c>
+      <c r="G35" s="4">
+        <v>360</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J35" s="1">
+        <v>8106</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>7</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="4">
+        <v>271</v>
+      </c>
+      <c r="G36" s="4">
+        <v>360</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J36" s="1">
+        <v>8107</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>8</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="4">
+        <v>271</v>
+      </c>
+      <c r="G37" s="4">
+        <v>360</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J37" s="1">
+        <v>8108</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:10">
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="8:9">
+    <row r="39" customHeight="1" spans="3:10">
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="8:9">
+    <row r="40" customHeight="1" spans="3:10">
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="8:9">
+    <row r="41" customHeight="1" spans="3:10">
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="8:9">
+    <row r="42" customHeight="1" spans="3:10">
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="8:9">
+    <row r="43" customHeight="1" spans="3:10">
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="8:9">
+    <row r="44" customHeight="1" spans="3:10">
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="8:9">
+    <row r="45" customHeight="1" spans="3:10">
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" customHeight="1" spans="8:9">
+    <row r="46" customHeight="1" spans="3:10">
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" customHeight="1" spans="8:9">
+    <row r="47" customHeight="1" spans="3:10">
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="8:9">
+    <row r="48" customHeight="1" spans="3:10">
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>

--- a/Excel/SoulBoneConfig.xlsx
+++ b/Excel/SoulBoneConfig.xlsx
@@ -212,10 +212,10 @@
     <t>14,15,16,18,20,19,24,2003,2002,2001,2013</t>
   </si>
   <si>
+    <t>10,10,10,1,1,0.5,0.5,0.1,0.08,0.07,0.05</t>
+  </si>
+  <si>
     <t>14,15,16,18,20,19,24,2004,2003,2001,2013</t>
-  </si>
-  <si>
-    <t>10,10,10,1,1,0.5,0.5,0.1,0.08,0.07,0.05</t>
   </si>
   <si>
     <t>14,15,16,18,20,19,24,2002,2001,2003,2013</t>
@@ -1953,7 +1953,7 @@
         <v>60</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J30" s="1">
         <v>8101</v>
@@ -1976,10 +1976,10 @@
         <v>360</v>
       </c>
       <c r="H31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="J31" s="1">
         <v>8102</v>
@@ -2005,7 +2005,7 @@
         <v>63</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J32" s="1">
         <v>8103</v>
@@ -2031,7 +2031,7 @@
         <v>60</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J33" s="1">
         <v>8104</v>
@@ -2057,7 +2057,7 @@
         <v>64</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J34" s="1">
         <v>8105</v>
@@ -2083,7 +2083,7 @@
         <v>65</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J35" s="1">
         <v>8106</v>
@@ -2109,7 +2109,7 @@
         <v>66</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J36" s="1">
         <v>8107</v>
@@ -2135,7 +2135,7 @@
         <v>67</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J37" s="1">
         <v>8108</v>
